--- a/static/standards-correlations/Maryland_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Maryland_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$38</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Maryland K-12 CS Standards, 9-10 band</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Maryland K-12 CS Standards, 9-10 band</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1062,7 +1063,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 10 covers phishing and why emotional pressure works. Ext 5.2D (Should It Exist?) requires a credible news source and explicitly rules out blogs and forums, which is the legitimate-versus-fraudulent half. Prevention is elementary-level only.</t>
+          <t>Introductory Systems 10 covers phishing and why emotional pressure works. Ext 5.2D (Should It Exist?) requires a credible news source and explicitly rules out blogs and forums, which is the legitimate-versus-fraudulent half. Prevention is elementary-level only.</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1748,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Botball Explorer is team-based by design. Unit 5.3 adds shared repositories and Discovery Systems 13 rotates defined roles.</t>
+          <t>Botball Explorer is team-based by design. Unit 5.3 adds shared repositories and Introductory Systems 13 rotates defined roles.</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1795,7 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Discovery Systems 4 teaches flowchart symbols, Ext 1.2B (Dependency Map) produces a node-and-arrow structure diagram, and Ext 5.1G (Write the Guide) plus Ext 5.3A (Write a Real README) supply the documentation.</t>
+          <t>Introductory Systems 4 teaches flowchart symbols, Ext 1.2B (Dependency Map) produces a node-and-arrow structure diagram, and Ext 5.1G (Write the Guide) plus Ext 5.3A (Write a Real README) supply the documentation.</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2022,7 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 13 asks what a team loses when one person always drives, which is the value-of-varied-input argument. Diversity in the broader sense is not addressed.</t>
+          <t>Introductory Systems 13 asks what a team loses when one person always drives, which is the value-of-varied-input argument. Diversity in the broader sense is not addressed.</t>
         </is>
       </c>
     </row>
@@ -2192,6 +2193,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -2236,7 +2238,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2250,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2348,6 +2350,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
@@ -2365,7 +2369,7 @@
 SOURCE NOTE: Standard codes and statements were transcribed from the CodeHS published Maryland 9-10 standards framework. HB 281 and the 2018 development start were verified against MSDE reporting. Verify wording against the official MSDE standards document before using this crosswalk in any formal submission.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.</t>
         </is>
       </c>
